--- a/Mod_Korean/Lang/KR/Dialog/Drama/namamani.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/namamani.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="namamani" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="namamani" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -70,9 +70,6 @@
     <t xml:space="preserve">What is this place?</t>
   </si>
   <si>
-    <t xml:space="preserve">뭐지, 이곳은?</t>
-  </si>
-  <si>
     <t xml:space="preserve">inject</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t xml:space="preserve">About miscreations.</t>
   </si>
   <si>
-    <t xml:space="preserve">실패작에 대해</t>
-  </si>
-  <si>
     <t xml:space="preserve">choice/bye</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve">You’re carrying  a curious machine. Let me take a look.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이상한 기계를 대동하고 있군. 잠시 보여줘 봐.</t>
   </si>
   <si>
     <t xml:space="preserve">…やはりな。回路の設計が甘い。信号の遅延、電流の揺らぎ、クロック歯車の同期精度、どれを取っても限界設計だ。これでは演算機関の潜在能力を半分も引き出せていない。
@@ -125,90 +116,102 @@
 ...Interesting. I can’t say I dislike this kind of rough craftsmanship. You got a memory chip on you?</t>
   </si>
   <si>
+    <t xml:space="preserve">miscreation_finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasItem,memory_chip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メモリーチップを渡す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand over the memory chip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">また次の機会に</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maybe later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失敗作？ 無能な技師の言い訳だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A miscreation? That’s just an excuse from an incompetent engineer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">build_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removeItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memory_chip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_miscreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…よし、これでいい。
+歯車同士が互いを讃えるような音。完璧な機械の鼓動だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...All right, that should do it.
+Hear that? The gears singing to each other—the heartbeat of a perfect machine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core_machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そうだ、こいつから取り外した古い部品をお前にやろう。記念に持っておいてやってくれ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here, take this old component I pulled out of it. Consider it a keepsake.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">뭐지, 이곳은?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실패작에 대해</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이상한 기계를 대동하고 있군. 잠시 보여줘 봐.</t>
+  </si>
+  <si>
     <t xml:space="preserve">…역시나. 회로 설계가 어설퍼. 신호에 딜레이가 있고, 전류도 불안정하고, 클록 톱니바퀴의 싱크 정밀도도 그렇고, 어느 것 하나 한계에 다다르지 않은 게 없군. 이래서는 연산기관의 잠재력을 절반도 못 살린다.
 도파관 배치도 난잡하고, 소음 방지 메커니즘도 없는 거나 다름없어. 기판을 다시 짜면 간섭이 꽤 경감될 텐데… 흠, 제어부의 쓰기 작업도 최적화를 할 여지가 있군. 기억 톱니바퀴 관리도 동적으로 하게 하면 처리 효율이 단숨에 상승할 거다.
 …딱히 이런 조잡한 기계를 싫어하진 않아. 혹시 메모리 칩 가진 것 있나?</t>
   </si>
   <si>
-    <t xml:space="preserve">miscreation_finish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasItem,memory_chip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メモリーチップを渡す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hand over the memory chip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">메모리 칩을 넘긴다</t>
   </si>
   <si>
-    <t xml:space="preserve">また次の機会に</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maybe later.</t>
-  </si>
-  <si>
     <t xml:space="preserve">다음 기회에</t>
   </si>
   <si>
-    <t xml:space="preserve">失敗作？ 無能な技師の言い訳だ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A miscreation? That’s just an excuse from an incompetent engineer.</t>
-  </si>
-  <si>
     <t xml:space="preserve">실패작? 그런 건 무능한 기술자나 하는 변명이지.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">build_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">removeItem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">memory_chip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_miscreation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…よし、これでいい。
-歯車同士が互いを讃えるような音。完璧な機械の鼓動だ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...All right, that should do it.
-Hear that? The gears singing to each other—the heartbeat of a perfect machine.</t>
   </si>
   <si>
     <t xml:space="preserve">…좋아, 이 정도면 됐다.
 톱니바퀴들이 서로를 칭송하는 듯한 소리. 완벽한 기계의 심장 고동이지.</t>
   </si>
   <si>
-    <t xml:space="preserve">drop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">core_machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">そうだ、こいつから取り外した古い部品をお前にやろう。記念に持っておいてやってくれ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here, take this old component I pulled out of it. Consider it a keepsake.</t>
-  </si>
-  <si>
     <t xml:space="preserve">아 맞다, 이 녀석한테서 뜯어낸 오래된 부품을 네게 넘기지. 기념으로 갖고 있어.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
   </si>
 </sst>
 </file>
@@ -218,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -229,20 +232,20 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
@@ -250,13 +253,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -274,7 +270,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -283,62 +279,54 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -352,13 +340,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -534,26 +522,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="46.42"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,275 +575,278 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="12.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
+      <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="1" t="s">
+    </row>
+    <row r="10" ht="12.8">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
+      <c r="E11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="2" t="s">
+    </row>
+    <row r="12" ht="12.8">
+      <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="1" t="s">
+    <row r="22" ht="12.8">
+      <c r="A22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="12.8">
+      <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="24" ht="12.8">
+      <c r="I24" s="1">
+        <v>3</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" ht="137.3">
+      <c r="I25" s="1">
+        <v>4</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" s="4" t="s">
+      <c r="I26" s="1">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="K26" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I27" s="1">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
       <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="1" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
+      <c r="I32" s="1">
         <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="B33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="A37" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="E38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" ht="12.8">
+      <c r="E39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" ht="12.8">
+      <c r="E40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" ht="43.25">
+      <c r="I41" s="1">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="L41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
+      <c r="E42" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="I42" s="1">
+        <v>9</v>
+      </c>
+      <c r="L42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" ht="12.8">
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E40" s="1" t="s">
+      <c r="K43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="L43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" ht="12.8">
+      <c r="E45" s="1" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="1" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I43" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="L43" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E45" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
